--- a/rcads/data/xls/23_InstrumentItemMap.xlsx
+++ b/rcads/data/xls/23_InstrumentItemMap.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_23_InstrumentItemMap"/>
   </sheets>
   <definedNames>
-    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$5295</definedName>
+    <definedName name="_23_InstrumentItemMap">'_23_InstrumentItemMap'!$A$1:$E$5625</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5295"/>
+  <dimension ref="A1:E5625"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -68910,7 +68910,7 @@
         <v>176</v>
       </c>
       <c r="C4835" s="0">
-        <v>3537</v>
+        <v>3583</v>
       </c>
       <c r="D4835" s="0">
         <v>1</v>
@@ -68938,7 +68938,7 @@
         <v>176</v>
       </c>
       <c r="C4837" s="0">
-        <v>3540</v>
+        <v>3585</v>
       </c>
       <c r="D4837" s="0">
         <v>3</v>
@@ -68952,7 +68952,7 @@
         <v>176</v>
       </c>
       <c r="C4838" s="0">
-        <v>3541</v>
+        <v>3586</v>
       </c>
       <c r="D4838" s="0">
         <v>4</v>
@@ -68966,7 +68966,7 @@
         <v>176</v>
       </c>
       <c r="C4839" s="0">
-        <v>3548</v>
+        <v>3587</v>
       </c>
       <c r="D4839" s="0">
         <v>5</v>
@@ -68980,7 +68980,7 @@
         <v>176</v>
       </c>
       <c r="C4840" s="0">
-        <v>3568</v>
+        <v>3588</v>
       </c>
       <c r="D4840" s="0">
         <v>6</v>
@@ -69008,7 +69008,7 @@
         <v>176</v>
       </c>
       <c r="C4842" s="0">
-        <v>3546</v>
+        <v>3590</v>
       </c>
       <c r="D4842" s="0">
         <v>8</v>
@@ -69022,7 +69022,7 @@
         <v>176</v>
       </c>
       <c r="C4843" s="0">
-        <v>3552</v>
+        <v>3591</v>
       </c>
       <c r="D4843" s="0">
         <v>9</v>
@@ -69036,7 +69036,7 @@
         <v>176</v>
       </c>
       <c r="C4844" s="0">
-        <v>3550</v>
+        <v>3592</v>
       </c>
       <c r="D4844" s="0">
         <v>10</v>
@@ -69050,7 +69050,7 @@
         <v>176</v>
       </c>
       <c r="C4845" s="0">
-        <v>3571</v>
+        <v>3593</v>
       </c>
       <c r="D4845" s="0">
         <v>11</v>
@@ -69064,7 +69064,7 @@
         <v>176</v>
       </c>
       <c r="C4846" s="0">
-        <v>3577</v>
+        <v>3594</v>
       </c>
       <c r="D4846" s="0">
         <v>12</v>
@@ -69092,7 +69092,7 @@
         <v>176</v>
       </c>
       <c r="C4848" s="0">
-        <v>3561</v>
+        <v>3596</v>
       </c>
       <c r="D4848" s="0">
         <v>14</v>
@@ -69106,7 +69106,7 @@
         <v>176</v>
       </c>
       <c r="C4849" s="0">
-        <v>3560</v>
+        <v>3597</v>
       </c>
       <c r="D4849" s="0">
         <v>15</v>
@@ -69148,7 +69148,7 @@
         <v>176</v>
       </c>
       <c r="C4852" s="0">
-        <v>3572</v>
+        <v>3600</v>
       </c>
       <c r="D4852" s="0">
         <v>18</v>
@@ -69162,7 +69162,7 @@
         <v>176</v>
       </c>
       <c r="C4853" s="0">
-        <v>3601</v>
+        <v>3596</v>
       </c>
       <c r="D4853" s="0">
         <v>19</v>
@@ -69190,7 +69190,7 @@
         <v>176</v>
       </c>
       <c r="C4855" s="0">
-        <v>3556</v>
+        <v>3603</v>
       </c>
       <c r="D4855" s="0">
         <v>21</v>
@@ -69218,7 +69218,7 @@
         <v>176</v>
       </c>
       <c r="C4857" s="0">
-        <v>3579</v>
+        <v>3605</v>
       </c>
       <c r="D4857" s="0">
         <v>23</v>
@@ -69246,7 +69246,7 @@
         <v>176</v>
       </c>
       <c r="C4859" s="0">
-        <v>3562</v>
+        <v>3607</v>
       </c>
       <c r="D4859" s="0">
         <v>25</v>
@@ -75354,6 +75354,4818 @@
       </c>
       <c r="D5295" s="0">
         <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5296">
+      <c r="A5296" s="0">
+        <v>6323</v>
+      </c>
+      <c r="B5296" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5296" s="0">
+        <v>3656</v>
+      </c>
+      <c r="D5296" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5297">
+      <c r="A5297" s="0">
+        <v>6324</v>
+      </c>
+      <c r="B5297" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5297" s="0">
+        <v>3660</v>
+      </c>
+      <c r="D5297" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5298">
+      <c r="A5298" s="0">
+        <v>6325</v>
+      </c>
+      <c r="B5298" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5298" s="0">
+        <v>3661</v>
+      </c>
+      <c r="D5298" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5299">
+      <c r="A5299" s="0">
+        <v>6326</v>
+      </c>
+      <c r="B5299" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5299" s="0">
+        <v>3663</v>
+      </c>
+      <c r="D5299" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5300">
+      <c r="A5300" s="0">
+        <v>6327</v>
+      </c>
+      <c r="B5300" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5300" s="0">
+        <v>3675</v>
+      </c>
+      <c r="D5300" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5301">
+      <c r="A5301" s="0">
+        <v>6328</v>
+      </c>
+      <c r="B5301" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5301" s="0">
+        <v>3706</v>
+      </c>
+      <c r="D5301" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5302">
+      <c r="A5302" s="0">
+        <v>6329</v>
+      </c>
+      <c r="B5302" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5302" s="0">
+        <v>3705</v>
+      </c>
+      <c r="D5302" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5303">
+      <c r="A5303" s="0">
+        <v>6330</v>
+      </c>
+      <c r="B5303" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5303" s="0">
+        <v>3673</v>
+      </c>
+      <c r="D5303" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5304">
+      <c r="A5304" s="0">
+        <v>6331</v>
+      </c>
+      <c r="B5304" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5304" s="0">
+        <v>3684</v>
+      </c>
+      <c r="D5304" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5305">
+      <c r="A5305" s="0">
+        <v>6332</v>
+      </c>
+      <c r="B5305" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5305" s="0">
+        <v>3680</v>
+      </c>
+      <c r="D5305" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5306">
+      <c r="A5306" s="0">
+        <v>6333</v>
+      </c>
+      <c r="B5306" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5306" s="0">
+        <v>3709</v>
+      </c>
+      <c r="D5306" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5307">
+      <c r="A5307" s="0">
+        <v>6334</v>
+      </c>
+      <c r="B5307" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5307" s="0">
+        <v>3715</v>
+      </c>
+      <c r="D5307" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5308">
+      <c r="A5308" s="0">
+        <v>6335</v>
+      </c>
+      <c r="B5308" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5308" s="0">
+        <v>3687</v>
+      </c>
+      <c r="D5308" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5309">
+      <c r="A5309" s="0">
+        <v>6336</v>
+      </c>
+      <c r="B5309" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5309" s="0">
+        <v>3698</v>
+      </c>
+      <c r="D5309" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5310">
+      <c r="A5310" s="0">
+        <v>6337</v>
+      </c>
+      <c r="B5310" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5310" s="0">
+        <v>3696</v>
+      </c>
+      <c r="D5310" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5311">
+      <c r="A5311" s="0">
+        <v>6338</v>
+      </c>
+      <c r="B5311" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5311" s="0">
+        <v>3702</v>
+      </c>
+      <c r="D5311" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5312">
+      <c r="A5312" s="0">
+        <v>6339</v>
+      </c>
+      <c r="B5312" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5312" s="0">
+        <v>3704</v>
+      </c>
+      <c r="D5312" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5313">
+      <c r="A5313" s="0">
+        <v>6340</v>
+      </c>
+      <c r="B5313" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5313" s="0">
+        <v>3710</v>
+      </c>
+      <c r="D5313" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5314">
+      <c r="A5314" s="0">
+        <v>6341</v>
+      </c>
+      <c r="B5314" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5314" s="0">
+        <v>3713</v>
+      </c>
+      <c r="D5314" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5315">
+      <c r="A5315" s="0">
+        <v>6342</v>
+      </c>
+      <c r="B5315" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5315" s="0">
+        <v>3714</v>
+      </c>
+      <c r="D5315" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5316">
+      <c r="A5316" s="0">
+        <v>6343</v>
+      </c>
+      <c r="B5316" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5316" s="0">
+        <v>3689</v>
+      </c>
+      <c r="D5316" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5317">
+      <c r="A5317" s="0">
+        <v>6344</v>
+      </c>
+      <c r="B5317" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5317" s="0">
+        <v>3716</v>
+      </c>
+      <c r="D5317" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5318">
+      <c r="A5318" s="0">
+        <v>6345</v>
+      </c>
+      <c r="B5318" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5318" s="0">
+        <v>3717</v>
+      </c>
+      <c r="D5318" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5319">
+      <c r="A5319" s="0">
+        <v>6346</v>
+      </c>
+      <c r="B5319" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5319" s="0">
+        <v>3720</v>
+      </c>
+      <c r="D5319" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5320">
+      <c r="A5320" s="0">
+        <v>6347</v>
+      </c>
+      <c r="B5320" s="0">
+        <v>122</v>
+      </c>
+      <c r="C5320" s="0">
+        <v>3699</v>
+      </c>
+      <c r="D5320" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5321">
+      <c r="A5321" s="0">
+        <v>6348</v>
+      </c>
+      <c r="B5321" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5321" s="0">
+        <v>3721</v>
+      </c>
+      <c r="D5321" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5322">
+      <c r="A5322" s="0">
+        <v>6349</v>
+      </c>
+      <c r="B5322" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5322" s="0">
+        <v>3722</v>
+      </c>
+      <c r="D5322" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5323">
+      <c r="A5323" s="0">
+        <v>6350</v>
+      </c>
+      <c r="B5323" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5323" s="0">
+        <v>3723</v>
+      </c>
+      <c r="D5323" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5324">
+      <c r="A5324" s="0">
+        <v>6351</v>
+      </c>
+      <c r="B5324" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5324" s="0">
+        <v>3724</v>
+      </c>
+      <c r="D5324" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5325">
+      <c r="A5325" s="0">
+        <v>6352</v>
+      </c>
+      <c r="B5325" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5325" s="0">
+        <v>3725</v>
+      </c>
+      <c r="D5325" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5326">
+      <c r="A5326" s="0">
+        <v>6353</v>
+      </c>
+      <c r="B5326" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5326" s="0">
+        <v>3726</v>
+      </c>
+      <c r="D5326" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5327">
+      <c r="A5327" s="0">
+        <v>6354</v>
+      </c>
+      <c r="B5327" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5327" s="0">
+        <v>3727</v>
+      </c>
+      <c r="D5327" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5328">
+      <c r="A5328" s="0">
+        <v>6355</v>
+      </c>
+      <c r="B5328" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5328" s="0">
+        <v>3728</v>
+      </c>
+      <c r="D5328" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5329">
+      <c r="A5329" s="0">
+        <v>6356</v>
+      </c>
+      <c r="B5329" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5329" s="0">
+        <v>3729</v>
+      </c>
+      <c r="D5329" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5330">
+      <c r="A5330" s="0">
+        <v>6357</v>
+      </c>
+      <c r="B5330" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5330" s="0">
+        <v>3730</v>
+      </c>
+      <c r="D5330" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5331">
+      <c r="A5331" s="0">
+        <v>6358</v>
+      </c>
+      <c r="B5331" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5331" s="0">
+        <v>3731</v>
+      </c>
+      <c r="D5331" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5332">
+      <c r="A5332" s="0">
+        <v>6359</v>
+      </c>
+      <c r="B5332" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5332" s="0">
+        <v>3732</v>
+      </c>
+      <c r="D5332" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5333">
+      <c r="A5333" s="0">
+        <v>6360</v>
+      </c>
+      <c r="B5333" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5333" s="0">
+        <v>3733</v>
+      </c>
+      <c r="D5333" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5334">
+      <c r="A5334" s="0">
+        <v>6361</v>
+      </c>
+      <c r="B5334" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5334" s="0">
+        <v>3734</v>
+      </c>
+      <c r="D5334" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5335">
+      <c r="A5335" s="0">
+        <v>6362</v>
+      </c>
+      <c r="B5335" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5335" s="0">
+        <v>3735</v>
+      </c>
+      <c r="D5335" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5336">
+      <c r="A5336" s="0">
+        <v>6363</v>
+      </c>
+      <c r="B5336" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5336" s="0">
+        <v>3736</v>
+      </c>
+      <c r="D5336" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5337">
+      <c r="A5337" s="0">
+        <v>6364</v>
+      </c>
+      <c r="B5337" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5337" s="0">
+        <v>3737</v>
+      </c>
+      <c r="D5337" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5338">
+      <c r="A5338" s="0">
+        <v>6365</v>
+      </c>
+      <c r="B5338" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5338" s="0">
+        <v>3738</v>
+      </c>
+      <c r="D5338" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5339">
+      <c r="A5339" s="0">
+        <v>6366</v>
+      </c>
+      <c r="B5339" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5339" s="0">
+        <v>3739</v>
+      </c>
+      <c r="D5339" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5340">
+      <c r="A5340" s="0">
+        <v>6367</v>
+      </c>
+      <c r="B5340" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5340" s="0">
+        <v>3740</v>
+      </c>
+      <c r="D5340" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5341">
+      <c r="A5341" s="0">
+        <v>6368</v>
+      </c>
+      <c r="B5341" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5341" s="0">
+        <v>3741</v>
+      </c>
+      <c r="D5341" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5342">
+      <c r="A5342" s="0">
+        <v>6369</v>
+      </c>
+      <c r="B5342" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5342" s="0">
+        <v>3742</v>
+      </c>
+      <c r="D5342" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5343">
+      <c r="A5343" s="0">
+        <v>6370</v>
+      </c>
+      <c r="B5343" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5343" s="0">
+        <v>3743</v>
+      </c>
+      <c r="D5343" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5344">
+      <c r="A5344" s="0">
+        <v>6371</v>
+      </c>
+      <c r="B5344" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5344" s="0">
+        <v>3744</v>
+      </c>
+      <c r="D5344" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5345">
+      <c r="A5345" s="0">
+        <v>6372</v>
+      </c>
+      <c r="B5345" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5345" s="0">
+        <v>3745</v>
+      </c>
+      <c r="D5345" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5346">
+      <c r="A5346" s="0">
+        <v>6373</v>
+      </c>
+      <c r="B5346" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5346" s="0">
+        <v>3746</v>
+      </c>
+      <c r="D5346" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5347">
+      <c r="A5347" s="0">
+        <v>6374</v>
+      </c>
+      <c r="B5347" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5347" s="0">
+        <v>3747</v>
+      </c>
+      <c r="D5347" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5348">
+      <c r="A5348" s="0">
+        <v>6375</v>
+      </c>
+      <c r="B5348" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5348" s="0">
+        <v>3748</v>
+      </c>
+      <c r="D5348" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5349">
+      <c r="A5349" s="0">
+        <v>6376</v>
+      </c>
+      <c r="B5349" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5349" s="0">
+        <v>3749</v>
+      </c>
+      <c r="D5349" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5350">
+      <c r="A5350" s="0">
+        <v>6377</v>
+      </c>
+      <c r="B5350" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5350" s="0">
+        <v>3750</v>
+      </c>
+      <c r="D5350" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5351">
+      <c r="A5351" s="0">
+        <v>6378</v>
+      </c>
+      <c r="B5351" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5351" s="0">
+        <v>3751</v>
+      </c>
+      <c r="D5351" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5352">
+      <c r="A5352" s="0">
+        <v>6379</v>
+      </c>
+      <c r="B5352" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5352" s="0">
+        <v>3752</v>
+      </c>
+      <c r="D5352" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5353">
+      <c r="A5353" s="0">
+        <v>6380</v>
+      </c>
+      <c r="B5353" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5353" s="0">
+        <v>3753</v>
+      </c>
+      <c r="D5353" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5354">
+      <c r="A5354" s="0">
+        <v>6381</v>
+      </c>
+      <c r="B5354" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5354" s="0">
+        <v>3754</v>
+      </c>
+      <c r="D5354" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5355">
+      <c r="A5355" s="0">
+        <v>6382</v>
+      </c>
+      <c r="B5355" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5355" s="0">
+        <v>3755</v>
+      </c>
+      <c r="D5355" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5356">
+      <c r="A5356" s="0">
+        <v>6383</v>
+      </c>
+      <c r="B5356" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5356" s="0">
+        <v>3756</v>
+      </c>
+      <c r="D5356" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5357">
+      <c r="A5357" s="0">
+        <v>6384</v>
+      </c>
+      <c r="B5357" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5357" s="0">
+        <v>3757</v>
+      </c>
+      <c r="D5357" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5358">
+      <c r="A5358" s="0">
+        <v>6385</v>
+      </c>
+      <c r="B5358" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5358" s="0">
+        <v>3758</v>
+      </c>
+      <c r="D5358" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5359">
+      <c r="A5359" s="0">
+        <v>6386</v>
+      </c>
+      <c r="B5359" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5359" s="0">
+        <v>3759</v>
+      </c>
+      <c r="D5359" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5360">
+      <c r="A5360" s="0">
+        <v>6387</v>
+      </c>
+      <c r="B5360" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5360" s="0">
+        <v>3760</v>
+      </c>
+      <c r="D5360" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5361">
+      <c r="A5361" s="0">
+        <v>6388</v>
+      </c>
+      <c r="B5361" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5361" s="0">
+        <v>3761</v>
+      </c>
+      <c r="D5361" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5362">
+      <c r="A5362" s="0">
+        <v>6389</v>
+      </c>
+      <c r="B5362" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5362" s="0">
+        <v>3762</v>
+      </c>
+      <c r="D5362" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5363">
+      <c r="A5363" s="0">
+        <v>6390</v>
+      </c>
+      <c r="B5363" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5363" s="0">
+        <v>3763</v>
+      </c>
+      <c r="D5363" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5364">
+      <c r="A5364" s="0">
+        <v>6391</v>
+      </c>
+      <c r="B5364" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5364" s="0">
+        <v>3764</v>
+      </c>
+      <c r="D5364" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5365">
+      <c r="A5365" s="0">
+        <v>6392</v>
+      </c>
+      <c r="B5365" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5365" s="0">
+        <v>3765</v>
+      </c>
+      <c r="D5365" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5366">
+      <c r="A5366" s="0">
+        <v>6393</v>
+      </c>
+      <c r="B5366" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5366" s="0">
+        <v>3766</v>
+      </c>
+      <c r="D5366" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5367">
+      <c r="A5367" s="0">
+        <v>6394</v>
+      </c>
+      <c r="B5367" s="0">
+        <v>116</v>
+      </c>
+      <c r="C5367" s="0">
+        <v>3767</v>
+      </c>
+      <c r="D5367" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5368">
+      <c r="A5368" s="0">
+        <v>6395</v>
+      </c>
+      <c r="B5368" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5368" s="0">
+        <v>3722</v>
+      </c>
+      <c r="D5368" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5369">
+      <c r="A5369" s="0">
+        <v>6396</v>
+      </c>
+      <c r="B5369" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5369" s="0">
+        <v>3724</v>
+      </c>
+      <c r="D5369" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5370">
+      <c r="A5370" s="0">
+        <v>6397</v>
+      </c>
+      <c r="B5370" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5370" s="0">
+        <v>3725</v>
+      </c>
+      <c r="D5370" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5371">
+      <c r="A5371" s="0">
+        <v>6398</v>
+      </c>
+      <c r="B5371" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5371" s="0">
+        <v>3726</v>
+      </c>
+      <c r="D5371" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5372">
+      <c r="A5372" s="0">
+        <v>6399</v>
+      </c>
+      <c r="B5372" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5372" s="0">
+        <v>3733</v>
+      </c>
+      <c r="D5372" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5373">
+      <c r="A5373" s="0">
+        <v>6400</v>
+      </c>
+      <c r="B5373" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5373" s="0">
+        <v>3753</v>
+      </c>
+      <c r="D5373" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5374">
+      <c r="A5374" s="0">
+        <v>6401</v>
+      </c>
+      <c r="B5374" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5374" s="0">
+        <v>3752</v>
+      </c>
+      <c r="D5374" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5375">
+      <c r="A5375" s="0">
+        <v>6402</v>
+      </c>
+      <c r="B5375" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5375" s="0">
+        <v>3731</v>
+      </c>
+      <c r="D5375" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5376">
+      <c r="A5376" s="0">
+        <v>6403</v>
+      </c>
+      <c r="B5376" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5376" s="0">
+        <v>3737</v>
+      </c>
+      <c r="D5376" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5377">
+      <c r="A5377" s="0">
+        <v>6404</v>
+      </c>
+      <c r="B5377" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5377" s="0">
+        <v>3735</v>
+      </c>
+      <c r="D5377" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5378">
+      <c r="A5378" s="0">
+        <v>6405</v>
+      </c>
+      <c r="B5378" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5378" s="0">
+        <v>3756</v>
+      </c>
+      <c r="D5378" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5379">
+      <c r="A5379" s="0">
+        <v>6406</v>
+      </c>
+      <c r="B5379" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5379" s="0">
+        <v>3762</v>
+      </c>
+      <c r="D5379" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5380">
+      <c r="A5380" s="0">
+        <v>6407</v>
+      </c>
+      <c r="B5380" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5380" s="0">
+        <v>3739</v>
+      </c>
+      <c r="D5380" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5381">
+      <c r="A5381" s="0">
+        <v>6408</v>
+      </c>
+      <c r="B5381" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5381" s="0">
+        <v>3746</v>
+      </c>
+      <c r="D5381" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5382">
+      <c r="A5382" s="0">
+        <v>6409</v>
+      </c>
+      <c r="B5382" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5382" s="0">
+        <v>3745</v>
+      </c>
+      <c r="D5382" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5383">
+      <c r="A5383" s="0">
+        <v>6410</v>
+      </c>
+      <c r="B5383" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5383" s="0">
+        <v>3749</v>
+      </c>
+      <c r="D5383" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5384">
+      <c r="A5384" s="0">
+        <v>6411</v>
+      </c>
+      <c r="B5384" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5384" s="0">
+        <v>3751</v>
+      </c>
+      <c r="D5384" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5385">
+      <c r="A5385" s="0">
+        <v>6412</v>
+      </c>
+      <c r="B5385" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5385" s="0">
+        <v>3757</v>
+      </c>
+      <c r="D5385" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5386">
+      <c r="A5386" s="0">
+        <v>6413</v>
+      </c>
+      <c r="B5386" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5386" s="0">
+        <v>3760</v>
+      </c>
+      <c r="D5386" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5387">
+      <c r="A5387" s="0">
+        <v>6414</v>
+      </c>
+      <c r="B5387" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5387" s="0">
+        <v>3761</v>
+      </c>
+      <c r="D5387" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5388">
+      <c r="A5388" s="0">
+        <v>6415</v>
+      </c>
+      <c r="B5388" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5388" s="0">
+        <v>3741</v>
+      </c>
+      <c r="D5388" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5389">
+      <c r="A5389" s="0">
+        <v>6416</v>
+      </c>
+      <c r="B5389" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5389" s="0">
+        <v>3763</v>
+      </c>
+      <c r="D5389" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5390">
+      <c r="A5390" s="0">
+        <v>6417</v>
+      </c>
+      <c r="B5390" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5390" s="0">
+        <v>3764</v>
+      </c>
+      <c r="D5390" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5391">
+      <c r="A5391" s="0">
+        <v>6418</v>
+      </c>
+      <c r="B5391" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5391" s="0">
+        <v>3767</v>
+      </c>
+      <c r="D5391" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5392">
+      <c r="A5392" s="0">
+        <v>6419</v>
+      </c>
+      <c r="B5392" s="0">
+        <v>118</v>
+      </c>
+      <c r="C5392" s="0">
+        <v>3747</v>
+      </c>
+      <c r="D5392" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5393">
+      <c r="A5393" s="0">
+        <v>6420</v>
+      </c>
+      <c r="B5393" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5393" s="0">
+        <v>3768</v>
+      </c>
+      <c r="D5393" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5394">
+      <c r="A5394" s="0">
+        <v>6421</v>
+      </c>
+      <c r="B5394" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5394" s="0">
+        <v>3769</v>
+      </c>
+      <c r="D5394" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5395">
+      <c r="A5395" s="0">
+        <v>6422</v>
+      </c>
+      <c r="B5395" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5395" s="0">
+        <v>3770</v>
+      </c>
+      <c r="D5395" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5396">
+      <c r="A5396" s="0">
+        <v>6423</v>
+      </c>
+      <c r="B5396" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5396" s="0">
+        <v>3771</v>
+      </c>
+      <c r="D5396" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5397">
+      <c r="A5397" s="0">
+        <v>6424</v>
+      </c>
+      <c r="B5397" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5397" s="0">
+        <v>3772</v>
+      </c>
+      <c r="D5397" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5398">
+      <c r="A5398" s="0">
+        <v>6425</v>
+      </c>
+      <c r="B5398" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5398" s="0">
+        <v>3773</v>
+      </c>
+      <c r="D5398" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5399">
+      <c r="A5399" s="0">
+        <v>6426</v>
+      </c>
+      <c r="B5399" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5399" s="0">
+        <v>3774</v>
+      </c>
+      <c r="D5399" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5400">
+      <c r="A5400" s="0">
+        <v>6427</v>
+      </c>
+      <c r="B5400" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5400" s="0">
+        <v>3775</v>
+      </c>
+      <c r="D5400" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5401">
+      <c r="A5401" s="0">
+        <v>6428</v>
+      </c>
+      <c r="B5401" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5401" s="0">
+        <v>3776</v>
+      </c>
+      <c r="D5401" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5402">
+      <c r="A5402" s="0">
+        <v>6429</v>
+      </c>
+      <c r="B5402" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5402" s="0">
+        <v>3777</v>
+      </c>
+      <c r="D5402" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5403">
+      <c r="A5403" s="0">
+        <v>6430</v>
+      </c>
+      <c r="B5403" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5403" s="0">
+        <v>3778</v>
+      </c>
+      <c r="D5403" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5404">
+      <c r="A5404" s="0">
+        <v>6431</v>
+      </c>
+      <c r="B5404" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5404" s="0">
+        <v>3779</v>
+      </c>
+      <c r="D5404" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5405">
+      <c r="A5405" s="0">
+        <v>6432</v>
+      </c>
+      <c r="B5405" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5405" s="0">
+        <v>3780</v>
+      </c>
+      <c r="D5405" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5406">
+      <c r="A5406" s="0">
+        <v>6433</v>
+      </c>
+      <c r="B5406" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5406" s="0">
+        <v>3781</v>
+      </c>
+      <c r="D5406" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5407">
+      <c r="A5407" s="0">
+        <v>6434</v>
+      </c>
+      <c r="B5407" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5407" s="0">
+        <v>3782</v>
+      </c>
+      <c r="D5407" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5408">
+      <c r="A5408" s="0">
+        <v>6435</v>
+      </c>
+      <c r="B5408" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5408" s="0">
+        <v>3783</v>
+      </c>
+      <c r="D5408" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5409">
+      <c r="A5409" s="0">
+        <v>6436</v>
+      </c>
+      <c r="B5409" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5409" s="0">
+        <v>3784</v>
+      </c>
+      <c r="D5409" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5410">
+      <c r="A5410" s="0">
+        <v>6437</v>
+      </c>
+      <c r="B5410" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5410" s="0">
+        <v>3785</v>
+      </c>
+      <c r="D5410" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5411">
+      <c r="A5411" s="0">
+        <v>6438</v>
+      </c>
+      <c r="B5411" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5411" s="0">
+        <v>3786</v>
+      </c>
+      <c r="D5411" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5412">
+      <c r="A5412" s="0">
+        <v>6439</v>
+      </c>
+      <c r="B5412" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5412" s="0">
+        <v>3787</v>
+      </c>
+      <c r="D5412" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5413">
+      <c r="A5413" s="0">
+        <v>6440</v>
+      </c>
+      <c r="B5413" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5413" s="0">
+        <v>3788</v>
+      </c>
+      <c r="D5413" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5414">
+      <c r="A5414" s="0">
+        <v>6441</v>
+      </c>
+      <c r="B5414" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5414" s="0">
+        <v>3789</v>
+      </c>
+      <c r="D5414" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5415">
+      <c r="A5415" s="0">
+        <v>6442</v>
+      </c>
+      <c r="B5415" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5415" s="0">
+        <v>3790</v>
+      </c>
+      <c r="D5415" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5416">
+      <c r="A5416" s="0">
+        <v>6443</v>
+      </c>
+      <c r="B5416" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5416" s="0">
+        <v>3791</v>
+      </c>
+      <c r="D5416" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5417">
+      <c r="A5417" s="0">
+        <v>6444</v>
+      </c>
+      <c r="B5417" s="0">
+        <v>126</v>
+      </c>
+      <c r="C5417" s="0">
+        <v>3792</v>
+      </c>
+      <c r="D5417" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5418">
+      <c r="A5418" s="0">
+        <v>6445</v>
+      </c>
+      <c r="B5418" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5418" s="0">
+        <v>3793</v>
+      </c>
+      <c r="D5418" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5419">
+      <c r="A5419" s="0">
+        <v>6446</v>
+      </c>
+      <c r="B5419" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5419" s="0">
+        <v>3794</v>
+      </c>
+      <c r="D5419" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5420">
+      <c r="A5420" s="0">
+        <v>6447</v>
+      </c>
+      <c r="B5420" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5420" s="0">
+        <v>3795</v>
+      </c>
+      <c r="D5420" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5421">
+      <c r="A5421" s="0">
+        <v>6448</v>
+      </c>
+      <c r="B5421" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5421" s="0">
+        <v>3796</v>
+      </c>
+      <c r="D5421" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5422">
+      <c r="A5422" s="0">
+        <v>6449</v>
+      </c>
+      <c r="B5422" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5422" s="0">
+        <v>3797</v>
+      </c>
+      <c r="D5422" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5423">
+      <c r="A5423" s="0">
+        <v>6450</v>
+      </c>
+      <c r="B5423" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5423" s="0">
+        <v>3798</v>
+      </c>
+      <c r="D5423" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5424">
+      <c r="A5424" s="0">
+        <v>6451</v>
+      </c>
+      <c r="B5424" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5424" s="0">
+        <v>3799</v>
+      </c>
+      <c r="D5424" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5425">
+      <c r="A5425" s="0">
+        <v>6452</v>
+      </c>
+      <c r="B5425" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5425" s="0">
+        <v>3800</v>
+      </c>
+      <c r="D5425" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5426">
+      <c r="A5426" s="0">
+        <v>6453</v>
+      </c>
+      <c r="B5426" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5426" s="0">
+        <v>3801</v>
+      </c>
+      <c r="D5426" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5427">
+      <c r="A5427" s="0">
+        <v>6454</v>
+      </c>
+      <c r="B5427" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5427" s="0">
+        <v>3802</v>
+      </c>
+      <c r="D5427" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5428">
+      <c r="A5428" s="0">
+        <v>6455</v>
+      </c>
+      <c r="B5428" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5428" s="0">
+        <v>3803</v>
+      </c>
+      <c r="D5428" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5429">
+      <c r="A5429" s="0">
+        <v>6456</v>
+      </c>
+      <c r="B5429" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5429" s="0">
+        <v>3804</v>
+      </c>
+      <c r="D5429" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5430">
+      <c r="A5430" s="0">
+        <v>6457</v>
+      </c>
+      <c r="B5430" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5430" s="0">
+        <v>3805</v>
+      </c>
+      <c r="D5430" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5431">
+      <c r="A5431" s="0">
+        <v>6458</v>
+      </c>
+      <c r="B5431" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5431" s="0">
+        <v>3806</v>
+      </c>
+      <c r="D5431" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5432">
+      <c r="A5432" s="0">
+        <v>6459</v>
+      </c>
+      <c r="B5432" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5432" s="0">
+        <v>3807</v>
+      </c>
+      <c r="D5432" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5433">
+      <c r="A5433" s="0">
+        <v>6460</v>
+      </c>
+      <c r="B5433" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5433" s="0">
+        <v>3808</v>
+      </c>
+      <c r="D5433" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5434">
+      <c r="A5434" s="0">
+        <v>6461</v>
+      </c>
+      <c r="B5434" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5434" s="0">
+        <v>3809</v>
+      </c>
+      <c r="D5434" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5435">
+      <c r="A5435" s="0">
+        <v>6462</v>
+      </c>
+      <c r="B5435" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5435" s="0">
+        <v>3810</v>
+      </c>
+      <c r="D5435" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5436">
+      <c r="A5436" s="0">
+        <v>6463</v>
+      </c>
+      <c r="B5436" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5436" s="0">
+        <v>3811</v>
+      </c>
+      <c r="D5436" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5437">
+      <c r="A5437" s="0">
+        <v>6464</v>
+      </c>
+      <c r="B5437" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5437" s="0">
+        <v>3812</v>
+      </c>
+      <c r="D5437" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5438">
+      <c r="A5438" s="0">
+        <v>6465</v>
+      </c>
+      <c r="B5438" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5438" s="0">
+        <v>3813</v>
+      </c>
+      <c r="D5438" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5439">
+      <c r="A5439" s="0">
+        <v>6466</v>
+      </c>
+      <c r="B5439" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5439" s="0">
+        <v>3814</v>
+      </c>
+      <c r="D5439" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5440">
+      <c r="A5440" s="0">
+        <v>6467</v>
+      </c>
+      <c r="B5440" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5440" s="0">
+        <v>3815</v>
+      </c>
+      <c r="D5440" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5441">
+      <c r="A5441" s="0">
+        <v>6468</v>
+      </c>
+      <c r="B5441" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5441" s="0">
+        <v>3816</v>
+      </c>
+      <c r="D5441" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5442">
+      <c r="A5442" s="0">
+        <v>6469</v>
+      </c>
+      <c r="B5442" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5442" s="0">
+        <v>3817</v>
+      </c>
+      <c r="D5442" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5443">
+      <c r="A5443" s="0">
+        <v>6470</v>
+      </c>
+      <c r="B5443" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5443" s="0">
+        <v>3818</v>
+      </c>
+      <c r="D5443" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5444">
+      <c r="A5444" s="0">
+        <v>6471</v>
+      </c>
+      <c r="B5444" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5444" s="0">
+        <v>3819</v>
+      </c>
+      <c r="D5444" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5445">
+      <c r="A5445" s="0">
+        <v>6472</v>
+      </c>
+      <c r="B5445" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5445" s="0">
+        <v>3820</v>
+      </c>
+      <c r="D5445" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5446">
+      <c r="A5446" s="0">
+        <v>6473</v>
+      </c>
+      <c r="B5446" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5446" s="0">
+        <v>3821</v>
+      </c>
+      <c r="D5446" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5447">
+      <c r="A5447" s="0">
+        <v>6474</v>
+      </c>
+      <c r="B5447" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5447" s="0">
+        <v>3822</v>
+      </c>
+      <c r="D5447" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5448">
+      <c r="A5448" s="0">
+        <v>6475</v>
+      </c>
+      <c r="B5448" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5448" s="0">
+        <v>3823</v>
+      </c>
+      <c r="D5448" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5449">
+      <c r="A5449" s="0">
+        <v>6476</v>
+      </c>
+      <c r="B5449" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5449" s="0">
+        <v>3824</v>
+      </c>
+      <c r="D5449" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5450">
+      <c r="A5450" s="0">
+        <v>6477</v>
+      </c>
+      <c r="B5450" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5450" s="0">
+        <v>3825</v>
+      </c>
+      <c r="D5450" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5451">
+      <c r="A5451" s="0">
+        <v>6478</v>
+      </c>
+      <c r="B5451" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5451" s="0">
+        <v>3826</v>
+      </c>
+      <c r="D5451" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5452">
+      <c r="A5452" s="0">
+        <v>6479</v>
+      </c>
+      <c r="B5452" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5452" s="0">
+        <v>3827</v>
+      </c>
+      <c r="D5452" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5453">
+      <c r="A5453" s="0">
+        <v>6480</v>
+      </c>
+      <c r="B5453" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5453" s="0">
+        <v>3828</v>
+      </c>
+      <c r="D5453" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5454">
+      <c r="A5454" s="0">
+        <v>6481</v>
+      </c>
+      <c r="B5454" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5454" s="0">
+        <v>3829</v>
+      </c>
+      <c r="D5454" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5455">
+      <c r="A5455" s="0">
+        <v>6482</v>
+      </c>
+      <c r="B5455" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5455" s="0">
+        <v>3830</v>
+      </c>
+      <c r="D5455" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5456">
+      <c r="A5456" s="0">
+        <v>6483</v>
+      </c>
+      <c r="B5456" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5456" s="0">
+        <v>3831</v>
+      </c>
+      <c r="D5456" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5457">
+      <c r="A5457" s="0">
+        <v>6484</v>
+      </c>
+      <c r="B5457" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5457" s="0">
+        <v>3832</v>
+      </c>
+      <c r="D5457" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5458">
+      <c r="A5458" s="0">
+        <v>6485</v>
+      </c>
+      <c r="B5458" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5458" s="0">
+        <v>3833</v>
+      </c>
+      <c r="D5458" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5459">
+      <c r="A5459" s="0">
+        <v>6486</v>
+      </c>
+      <c r="B5459" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5459" s="0">
+        <v>3886</v>
+      </c>
+      <c r="D5459" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5460">
+      <c r="A5460" s="0">
+        <v>6487</v>
+      </c>
+      <c r="B5460" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5460" s="0">
+        <v>3834</v>
+      </c>
+      <c r="D5460" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5461">
+      <c r="A5461" s="0">
+        <v>6488</v>
+      </c>
+      <c r="B5461" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5461" s="0">
+        <v>3835</v>
+      </c>
+      <c r="D5461" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5462">
+      <c r="A5462" s="0">
+        <v>6489</v>
+      </c>
+      <c r="B5462" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5462" s="0">
+        <v>3836</v>
+      </c>
+      <c r="D5462" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5463">
+      <c r="A5463" s="0">
+        <v>6490</v>
+      </c>
+      <c r="B5463" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5463" s="0">
+        <v>3837</v>
+      </c>
+      <c r="D5463" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5464">
+      <c r="A5464" s="0">
+        <v>6491</v>
+      </c>
+      <c r="B5464" s="0">
+        <v>177</v>
+      </c>
+      <c r="C5464" s="0">
+        <v>3838</v>
+      </c>
+      <c r="D5464" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5465">
+      <c r="A5465" s="0">
+        <v>6492</v>
+      </c>
+      <c r="B5465" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5465" s="0">
+        <v>3839</v>
+      </c>
+      <c r="D5465" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5466">
+      <c r="A5466" s="0">
+        <v>6493</v>
+      </c>
+      <c r="B5466" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5466" s="0">
+        <v>3840</v>
+      </c>
+      <c r="D5466" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5467">
+      <c r="A5467" s="0">
+        <v>6494</v>
+      </c>
+      <c r="B5467" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5467" s="0">
+        <v>3841</v>
+      </c>
+      <c r="D5467" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5468">
+      <c r="A5468" s="0">
+        <v>6495</v>
+      </c>
+      <c r="B5468" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5468" s="0">
+        <v>3842</v>
+      </c>
+      <c r="D5468" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5469">
+      <c r="A5469" s="0">
+        <v>6496</v>
+      </c>
+      <c r="B5469" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5469" s="0">
+        <v>3843</v>
+      </c>
+      <c r="D5469" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5470">
+      <c r="A5470" s="0">
+        <v>6497</v>
+      </c>
+      <c r="B5470" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5470" s="0">
+        <v>3844</v>
+      </c>
+      <c r="D5470" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5471">
+      <c r="A5471" s="0">
+        <v>6498</v>
+      </c>
+      <c r="B5471" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5471" s="0">
+        <v>3845</v>
+      </c>
+      <c r="D5471" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5472">
+      <c r="A5472" s="0">
+        <v>6499</v>
+      </c>
+      <c r="B5472" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5472" s="0">
+        <v>3846</v>
+      </c>
+      <c r="D5472" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5473">
+      <c r="A5473" s="0">
+        <v>6500</v>
+      </c>
+      <c r="B5473" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5473" s="0">
+        <v>3847</v>
+      </c>
+      <c r="D5473" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5474">
+      <c r="A5474" s="0">
+        <v>6501</v>
+      </c>
+      <c r="B5474" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5474" s="0">
+        <v>3848</v>
+      </c>
+      <c r="D5474" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5475">
+      <c r="A5475" s="0">
+        <v>6502</v>
+      </c>
+      <c r="B5475" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5475" s="0">
+        <v>3849</v>
+      </c>
+      <c r="D5475" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5476">
+      <c r="A5476" s="0">
+        <v>6503</v>
+      </c>
+      <c r="B5476" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5476" s="0">
+        <v>3850</v>
+      </c>
+      <c r="D5476" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5477">
+      <c r="A5477" s="0">
+        <v>6504</v>
+      </c>
+      <c r="B5477" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5477" s="0">
+        <v>3851</v>
+      </c>
+      <c r="D5477" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5478">
+      <c r="A5478" s="0">
+        <v>6505</v>
+      </c>
+      <c r="B5478" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5478" s="0">
+        <v>3852</v>
+      </c>
+      <c r="D5478" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5479">
+      <c r="A5479" s="0">
+        <v>6506</v>
+      </c>
+      <c r="B5479" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5479" s="0">
+        <v>3853</v>
+      </c>
+      <c r="D5479" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5480">
+      <c r="A5480" s="0">
+        <v>6507</v>
+      </c>
+      <c r="B5480" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5480" s="0">
+        <v>3854</v>
+      </c>
+      <c r="D5480" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5481">
+      <c r="A5481" s="0">
+        <v>6508</v>
+      </c>
+      <c r="B5481" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5481" s="0">
+        <v>3855</v>
+      </c>
+      <c r="D5481" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5482">
+      <c r="A5482" s="0">
+        <v>6509</v>
+      </c>
+      <c r="B5482" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5482" s="0">
+        <v>3856</v>
+      </c>
+      <c r="D5482" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5483">
+      <c r="A5483" s="0">
+        <v>6510</v>
+      </c>
+      <c r="B5483" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5483" s="0">
+        <v>3857</v>
+      </c>
+      <c r="D5483" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5484">
+      <c r="A5484" s="0">
+        <v>6511</v>
+      </c>
+      <c r="B5484" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5484" s="0">
+        <v>3858</v>
+      </c>
+      <c r="D5484" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5485">
+      <c r="A5485" s="0">
+        <v>6512</v>
+      </c>
+      <c r="B5485" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5485" s="0">
+        <v>3859</v>
+      </c>
+      <c r="D5485" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5486">
+      <c r="A5486" s="0">
+        <v>6513</v>
+      </c>
+      <c r="B5486" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5486" s="0">
+        <v>3860</v>
+      </c>
+      <c r="D5486" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5487">
+      <c r="A5487" s="0">
+        <v>6514</v>
+      </c>
+      <c r="B5487" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5487" s="0">
+        <v>3861</v>
+      </c>
+      <c r="D5487" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5488">
+      <c r="A5488" s="0">
+        <v>6515</v>
+      </c>
+      <c r="B5488" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5488" s="0">
+        <v>3862</v>
+      </c>
+      <c r="D5488" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5489">
+      <c r="A5489" s="0">
+        <v>6516</v>
+      </c>
+      <c r="B5489" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5489" s="0">
+        <v>3863</v>
+      </c>
+      <c r="D5489" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5490">
+      <c r="A5490" s="0">
+        <v>6517</v>
+      </c>
+      <c r="B5490" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5490" s="0">
+        <v>3864</v>
+      </c>
+      <c r="D5490" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5491">
+      <c r="A5491" s="0">
+        <v>6518</v>
+      </c>
+      <c r="B5491" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5491" s="0">
+        <v>3865</v>
+      </c>
+      <c r="D5491" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5492">
+      <c r="A5492" s="0">
+        <v>6519</v>
+      </c>
+      <c r="B5492" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5492" s="0">
+        <v>3866</v>
+      </c>
+      <c r="D5492" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5493">
+      <c r="A5493" s="0">
+        <v>6520</v>
+      </c>
+      <c r="B5493" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5493" s="0">
+        <v>3867</v>
+      </c>
+      <c r="D5493" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5494">
+      <c r="A5494" s="0">
+        <v>6521</v>
+      </c>
+      <c r="B5494" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5494" s="0">
+        <v>3868</v>
+      </c>
+      <c r="D5494" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5495">
+      <c r="A5495" s="0">
+        <v>6522</v>
+      </c>
+      <c r="B5495" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5495" s="0">
+        <v>3869</v>
+      </c>
+      <c r="D5495" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5496">
+      <c r="A5496" s="0">
+        <v>6523</v>
+      </c>
+      <c r="B5496" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5496" s="0">
+        <v>3870</v>
+      </c>
+      <c r="D5496" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5497">
+      <c r="A5497" s="0">
+        <v>6524</v>
+      </c>
+      <c r="B5497" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5497" s="0">
+        <v>3871</v>
+      </c>
+      <c r="D5497" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5498">
+      <c r="A5498" s="0">
+        <v>6525</v>
+      </c>
+      <c r="B5498" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5498" s="0">
+        <v>3872</v>
+      </c>
+      <c r="D5498" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5499">
+      <c r="A5499" s="0">
+        <v>6526</v>
+      </c>
+      <c r="B5499" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5499" s="0">
+        <v>3873</v>
+      </c>
+      <c r="D5499" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5500">
+      <c r="A5500" s="0">
+        <v>6527</v>
+      </c>
+      <c r="B5500" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5500" s="0">
+        <v>3874</v>
+      </c>
+      <c r="D5500" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5501">
+      <c r="A5501" s="0">
+        <v>6528</v>
+      </c>
+      <c r="B5501" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5501" s="0">
+        <v>3875</v>
+      </c>
+      <c r="D5501" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5502">
+      <c r="A5502" s="0">
+        <v>6529</v>
+      </c>
+      <c r="B5502" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5502" s="0">
+        <v>3876</v>
+      </c>
+      <c r="D5502" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5503">
+      <c r="A5503" s="0">
+        <v>6530</v>
+      </c>
+      <c r="B5503" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5503" s="0">
+        <v>3877</v>
+      </c>
+      <c r="D5503" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5504">
+      <c r="A5504" s="0">
+        <v>6531</v>
+      </c>
+      <c r="B5504" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5504" s="0">
+        <v>3878</v>
+      </c>
+      <c r="D5504" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5505">
+      <c r="A5505" s="0">
+        <v>6532</v>
+      </c>
+      <c r="B5505" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5505" s="0">
+        <v>3879</v>
+      </c>
+      <c r="D5505" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5506">
+      <c r="A5506" s="0">
+        <v>6533</v>
+      </c>
+      <c r="B5506" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5506" s="0">
+        <v>3880</v>
+      </c>
+      <c r="D5506" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5507">
+      <c r="A5507" s="0">
+        <v>6534</v>
+      </c>
+      <c r="B5507" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5507" s="0">
+        <v>3881</v>
+      </c>
+      <c r="D5507" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5508">
+      <c r="A5508" s="0">
+        <v>6535</v>
+      </c>
+      <c r="B5508" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5508" s="0">
+        <v>3882</v>
+      </c>
+      <c r="D5508" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5509">
+      <c r="A5509" s="0">
+        <v>6536</v>
+      </c>
+      <c r="B5509" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5509" s="0">
+        <v>3883</v>
+      </c>
+      <c r="D5509" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5510">
+      <c r="A5510" s="0">
+        <v>6537</v>
+      </c>
+      <c r="B5510" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5510" s="0">
+        <v>3884</v>
+      </c>
+      <c r="D5510" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5511">
+      <c r="A5511" s="0">
+        <v>6538</v>
+      </c>
+      <c r="B5511" s="0">
+        <v>178</v>
+      </c>
+      <c r="C5511" s="0">
+        <v>3885</v>
+      </c>
+      <c r="D5511" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5512">
+      <c r="A5512" s="0">
+        <v>6539</v>
+      </c>
+      <c r="B5512" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5512" s="0">
+        <v>3794</v>
+      </c>
+      <c r="D5512" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5513">
+      <c r="A5513" s="0">
+        <v>6540</v>
+      </c>
+      <c r="B5513" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5513" s="0">
+        <v>3796</v>
+      </c>
+      <c r="D5513" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5514">
+      <c r="A5514" s="0">
+        <v>6541</v>
+      </c>
+      <c r="B5514" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5514" s="0">
+        <v>3797</v>
+      </c>
+      <c r="D5514" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5515">
+      <c r="A5515" s="0">
+        <v>6542</v>
+      </c>
+      <c r="B5515" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5515" s="0">
+        <v>3798</v>
+      </c>
+      <c r="D5515" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5516">
+      <c r="A5516" s="0">
+        <v>6543</v>
+      </c>
+      <c r="B5516" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5516" s="0">
+        <v>3805</v>
+      </c>
+      <c r="D5516" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5517">
+      <c r="A5517" s="0">
+        <v>6544</v>
+      </c>
+      <c r="B5517" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5517" s="0">
+        <v>3825</v>
+      </c>
+      <c r="D5517" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5518">
+      <c r="A5518" s="0">
+        <v>6545</v>
+      </c>
+      <c r="B5518" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5518" s="0">
+        <v>3824</v>
+      </c>
+      <c r="D5518" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5519">
+      <c r="A5519" s="0">
+        <v>6546</v>
+      </c>
+      <c r="B5519" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5519" s="0">
+        <v>3803</v>
+      </c>
+      <c r="D5519" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5520">
+      <c r="A5520" s="0">
+        <v>6547</v>
+      </c>
+      <c r="B5520" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5520" s="0">
+        <v>3809</v>
+      </c>
+      <c r="D5520" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5521">
+      <c r="A5521" s="0">
+        <v>6548</v>
+      </c>
+      <c r="B5521" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5521" s="0">
+        <v>3807</v>
+      </c>
+      <c r="D5521" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5522">
+      <c r="A5522" s="0">
+        <v>6549</v>
+      </c>
+      <c r="B5522" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5522" s="0">
+        <v>3828</v>
+      </c>
+      <c r="D5522" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5523">
+      <c r="A5523" s="0">
+        <v>6550</v>
+      </c>
+      <c r="B5523" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5523" s="0">
+        <v>3886</v>
+      </c>
+      <c r="D5523" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5524">
+      <c r="A5524" s="0">
+        <v>6551</v>
+      </c>
+      <c r="B5524" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5524" s="0">
+        <v>3811</v>
+      </c>
+      <c r="D5524" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5525">
+      <c r="A5525" s="0">
+        <v>6552</v>
+      </c>
+      <c r="B5525" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5525" s="0">
+        <v>3818</v>
+      </c>
+      <c r="D5525" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5526">
+      <c r="A5526" s="0">
+        <v>6553</v>
+      </c>
+      <c r="B5526" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5526" s="0">
+        <v>3817</v>
+      </c>
+      <c r="D5526" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5527">
+      <c r="A5527" s="0">
+        <v>6554</v>
+      </c>
+      <c r="B5527" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5527" s="0">
+        <v>3821</v>
+      </c>
+      <c r="D5527" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5528">
+      <c r="A5528" s="0">
+        <v>6555</v>
+      </c>
+      <c r="B5528" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5528" s="0">
+        <v>3823</v>
+      </c>
+      <c r="D5528" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5529">
+      <c r="A5529" s="0">
+        <v>6556</v>
+      </c>
+      <c r="B5529" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5529" s="0">
+        <v>3829</v>
+      </c>
+      <c r="D5529" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5530">
+      <c r="A5530" s="0">
+        <v>6557</v>
+      </c>
+      <c r="B5530" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5530" s="0">
+        <v>3832</v>
+      </c>
+      <c r="D5530" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5531">
+      <c r="A5531" s="0">
+        <v>6558</v>
+      </c>
+      <c r="B5531" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5531" s="0">
+        <v>3833</v>
+      </c>
+      <c r="D5531" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5532">
+      <c r="A5532" s="0">
+        <v>6559</v>
+      </c>
+      <c r="B5532" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5532" s="0">
+        <v>3813</v>
+      </c>
+      <c r="D5532" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5533">
+      <c r="A5533" s="0">
+        <v>6560</v>
+      </c>
+      <c r="B5533" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5533" s="0">
+        <v>3834</v>
+      </c>
+      <c r="D5533" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5534">
+      <c r="A5534" s="0">
+        <v>6561</v>
+      </c>
+      <c r="B5534" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5534" s="0">
+        <v>3835</v>
+      </c>
+      <c r="D5534" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5535">
+      <c r="A5535" s="0">
+        <v>6562</v>
+      </c>
+      <c r="B5535" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5535" s="0">
+        <v>3838</v>
+      </c>
+      <c r="D5535" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5536">
+      <c r="A5536" s="0">
+        <v>6563</v>
+      </c>
+      <c r="B5536" s="0">
+        <v>179</v>
+      </c>
+      <c r="C5536" s="0">
+        <v>3819</v>
+      </c>
+      <c r="D5536" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5537">
+      <c r="A5537" s="0">
+        <v>6564</v>
+      </c>
+      <c r="B5537" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5537" s="0">
+        <v>3840</v>
+      </c>
+      <c r="D5537" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5538">
+      <c r="A5538" s="0">
+        <v>6565</v>
+      </c>
+      <c r="B5538" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5538" s="0">
+        <v>3842</v>
+      </c>
+      <c r="D5538" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5539">
+      <c r="A5539" s="0">
+        <v>6566</v>
+      </c>
+      <c r="B5539" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5539" s="0">
+        <v>3843</v>
+      </c>
+      <c r="D5539" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5540">
+      <c r="A5540" s="0">
+        <v>6567</v>
+      </c>
+      <c r="B5540" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5540" s="0">
+        <v>3844</v>
+      </c>
+      <c r="D5540" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5541">
+      <c r="A5541" s="0">
+        <v>6568</v>
+      </c>
+      <c r="B5541" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5541" s="0">
+        <v>3851</v>
+      </c>
+      <c r="D5541" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5542">
+      <c r="A5542" s="0">
+        <v>6569</v>
+      </c>
+      <c r="B5542" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5542" s="0">
+        <v>3871</v>
+      </c>
+      <c r="D5542" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5543">
+      <c r="A5543" s="0">
+        <v>6570</v>
+      </c>
+      <c r="B5543" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5543" s="0">
+        <v>3870</v>
+      </c>
+      <c r="D5543" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5544">
+      <c r="A5544" s="0">
+        <v>6571</v>
+      </c>
+      <c r="B5544" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5544" s="0">
+        <v>3849</v>
+      </c>
+      <c r="D5544" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5545">
+      <c r="A5545" s="0">
+        <v>6572</v>
+      </c>
+      <c r="B5545" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5545" s="0">
+        <v>3855</v>
+      </c>
+      <c r="D5545" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5546">
+      <c r="A5546" s="0">
+        <v>6573</v>
+      </c>
+      <c r="B5546" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5546" s="0">
+        <v>3853</v>
+      </c>
+      <c r="D5546" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5547">
+      <c r="A5547" s="0">
+        <v>6574</v>
+      </c>
+      <c r="B5547" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5547" s="0">
+        <v>3874</v>
+      </c>
+      <c r="D5547" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5548">
+      <c r="A5548" s="0">
+        <v>6575</v>
+      </c>
+      <c r="B5548" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5548" s="0">
+        <v>3880</v>
+      </c>
+      <c r="D5548" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5549">
+      <c r="A5549" s="0">
+        <v>6576</v>
+      </c>
+      <c r="B5549" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5549" s="0">
+        <v>3857</v>
+      </c>
+      <c r="D5549" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5550">
+      <c r="A5550" s="0">
+        <v>6577</v>
+      </c>
+      <c r="B5550" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5550" s="0">
+        <v>3864</v>
+      </c>
+      <c r="D5550" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5551">
+      <c r="A5551" s="0">
+        <v>6578</v>
+      </c>
+      <c r="B5551" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5551" s="0">
+        <v>3863</v>
+      </c>
+      <c r="D5551" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5552">
+      <c r="A5552" s="0">
+        <v>6579</v>
+      </c>
+      <c r="B5552" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5552" s="0">
+        <v>3867</v>
+      </c>
+      <c r="D5552" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5553">
+      <c r="A5553" s="0">
+        <v>6580</v>
+      </c>
+      <c r="B5553" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5553" s="0">
+        <v>3869</v>
+      </c>
+      <c r="D5553" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5554">
+      <c r="A5554" s="0">
+        <v>6581</v>
+      </c>
+      <c r="B5554" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5554" s="0">
+        <v>3875</v>
+      </c>
+      <c r="D5554" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5555">
+      <c r="A5555" s="0">
+        <v>6582</v>
+      </c>
+      <c r="B5555" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5555" s="0">
+        <v>3878</v>
+      </c>
+      <c r="D5555" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5556">
+      <c r="A5556" s="0">
+        <v>6583</v>
+      </c>
+      <c r="B5556" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5556" s="0">
+        <v>3879</v>
+      </c>
+      <c r="D5556" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5557">
+      <c r="A5557" s="0">
+        <v>6584</v>
+      </c>
+      <c r="B5557" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5557" s="0">
+        <v>3859</v>
+      </c>
+      <c r="D5557" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5558">
+      <c r="A5558" s="0">
+        <v>6585</v>
+      </c>
+      <c r="B5558" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5558" s="0">
+        <v>3881</v>
+      </c>
+      <c r="D5558" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5559">
+      <c r="A5559" s="0">
+        <v>6586</v>
+      </c>
+      <c r="B5559" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5559" s="0">
+        <v>3882</v>
+      </c>
+      <c r="D5559" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5560">
+      <c r="A5560" s="0">
+        <v>6587</v>
+      </c>
+      <c r="B5560" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5560" s="0">
+        <v>3885</v>
+      </c>
+      <c r="D5560" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5561">
+      <c r="A5561" s="0">
+        <v>6588</v>
+      </c>
+      <c r="B5561" s="0">
+        <v>180</v>
+      </c>
+      <c r="C5561" s="0">
+        <v>3865</v>
+      </c>
+      <c r="D5561" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5562">
+      <c r="A5562" s="0">
+        <v>6589</v>
+      </c>
+      <c r="B5562" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5562" s="0">
+        <v>2140</v>
+      </c>
+      <c r="D5562" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5562" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5563">
+      <c r="A5563" s="0">
+        <v>6590</v>
+      </c>
+      <c r="B5563" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5563" s="0">
+        <v>2141</v>
+      </c>
+      <c r="D5563" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5563" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5564">
+      <c r="A5564" s="0">
+        <v>6591</v>
+      </c>
+      <c r="B5564" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5564" s="0">
+        <v>2142</v>
+      </c>
+      <c r="D5564" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5564" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5565">
+      <c r="A5565" s="0">
+        <v>6592</v>
+      </c>
+      <c r="B5565" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5565" s="0">
+        <v>2143</v>
+      </c>
+      <c r="D5565" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5565" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5566">
+      <c r="A5566" s="0">
+        <v>6593</v>
+      </c>
+      <c r="B5566" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5566" s="0">
+        <v>2144</v>
+      </c>
+      <c r="D5566" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5566" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5567">
+      <c r="A5567" s="0">
+        <v>6594</v>
+      </c>
+      <c r="B5567" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5567" s="0">
+        <v>2145</v>
+      </c>
+      <c r="D5567" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5567" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5568">
+      <c r="A5568" s="0">
+        <v>6595</v>
+      </c>
+      <c r="B5568" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5568" s="0">
+        <v>2146</v>
+      </c>
+      <c r="D5568" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5568" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5569">
+      <c r="A5569" s="0">
+        <v>6596</v>
+      </c>
+      <c r="B5569" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5569" s="0">
+        <v>3887</v>
+      </c>
+      <c r="D5569" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5569" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5570">
+      <c r="A5570" s="0">
+        <v>6597</v>
+      </c>
+      <c r="B5570" s="0">
+        <v>181</v>
+      </c>
+      <c r="C5570" s="0">
+        <v>2148</v>
+      </c>
+      <c r="D5570" s="0">
+        <v>9</v>
+      </c>
+      <c r="E5570" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5571">
+      <c r="A5571" s="0">
+        <v>6598</v>
+      </c>
+      <c r="B5571" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5571" s="0">
+        <v>2140</v>
+      </c>
+      <c r="D5571" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5571" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5572">
+      <c r="A5572" s="0">
+        <v>6599</v>
+      </c>
+      <c r="B5572" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5572" s="0">
+        <v>2141</v>
+      </c>
+      <c r="D5572" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5572" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5573">
+      <c r="A5573" s="0">
+        <v>6600</v>
+      </c>
+      <c r="B5573" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5573" s="0">
+        <v>2142</v>
+      </c>
+      <c r="D5573" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5573" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5574">
+      <c r="A5574" s="0">
+        <v>6601</v>
+      </c>
+      <c r="B5574" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5574" s="0">
+        <v>2143</v>
+      </c>
+      <c r="D5574" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5574" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5575">
+      <c r="A5575" s="0">
+        <v>6602</v>
+      </c>
+      <c r="B5575" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5575" s="0">
+        <v>2144</v>
+      </c>
+      <c r="D5575" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5575" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5576">
+      <c r="A5576" s="0">
+        <v>6603</v>
+      </c>
+      <c r="B5576" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5576" s="0">
+        <v>2145</v>
+      </c>
+      <c r="D5576" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5576" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5577">
+      <c r="A5577" s="0">
+        <v>6604</v>
+      </c>
+      <c r="B5577" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5577" s="0">
+        <v>2146</v>
+      </c>
+      <c r="D5577" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5577" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5578">
+      <c r="A5578" s="0">
+        <v>6605</v>
+      </c>
+      <c r="B5578" s="0">
+        <v>182</v>
+      </c>
+      <c r="C5578" s="0">
+        <v>2147</v>
+      </c>
+      <c r="D5578" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5578" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5579">
+      <c r="A5579" s="0">
+        <v>6606</v>
+      </c>
+      <c r="B5579" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5579" s="0">
+        <v>3888</v>
+      </c>
+      <c r="D5579" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5579" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5580">
+      <c r="A5580" s="0">
+        <v>6607</v>
+      </c>
+      <c r="B5580" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5580" s="0">
+        <v>2140</v>
+      </c>
+      <c r="D5580" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5580" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5581">
+      <c r="A5581" s="0">
+        <v>6608</v>
+      </c>
+      <c r="B5581" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5581" s="0">
+        <v>2141</v>
+      </c>
+      <c r="D5581" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5581" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5582">
+      <c r="A5582" s="0">
+        <v>6609</v>
+      </c>
+      <c r="B5582" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5582" s="0">
+        <v>2142</v>
+      </c>
+      <c r="D5582" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5582" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5583">
+      <c r="A5583" s="0">
+        <v>6610</v>
+      </c>
+      <c r="B5583" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5583" s="0">
+        <v>2143</v>
+      </c>
+      <c r="D5583" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5583" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5584">
+      <c r="A5584" s="0">
+        <v>6611</v>
+      </c>
+      <c r="B5584" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5584" s="0">
+        <v>2144</v>
+      </c>
+      <c r="D5584" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5584" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5585">
+      <c r="A5585" s="0">
+        <v>6612</v>
+      </c>
+      <c r="B5585" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5585" s="0">
+        <v>2145</v>
+      </c>
+      <c r="D5585" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5585" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5586">
+      <c r="A5586" s="0">
+        <v>6613</v>
+      </c>
+      <c r="B5586" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5586" s="0">
+        <v>2146</v>
+      </c>
+      <c r="D5586" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5586" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5587">
+      <c r="A5587" s="0">
+        <v>6614</v>
+      </c>
+      <c r="B5587" s="0">
+        <v>183</v>
+      </c>
+      <c r="C5587" s="0">
+        <v>3887</v>
+      </c>
+      <c r="D5587" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5587" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5588">
+      <c r="A5588" s="0">
+        <v>6615</v>
+      </c>
+      <c r="B5588" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5588" s="0">
+        <v>3888</v>
+      </c>
+      <c r="D5588" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5588" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5589">
+      <c r="A5589" s="0">
+        <v>6616</v>
+      </c>
+      <c r="B5589" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5589" s="0">
+        <v>3889</v>
+      </c>
+      <c r="D5589" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5589" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5590">
+      <c r="A5590" s="0">
+        <v>6617</v>
+      </c>
+      <c r="B5590" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5590" s="0">
+        <v>3890</v>
+      </c>
+      <c r="D5590" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5590" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5591">
+      <c r="A5591" s="0">
+        <v>6618</v>
+      </c>
+      <c r="B5591" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5591" s="0">
+        <v>3891</v>
+      </c>
+      <c r="D5591" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5591" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5592">
+      <c r="A5592" s="0">
+        <v>6619</v>
+      </c>
+      <c r="B5592" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5592" s="0">
+        <v>3892</v>
+      </c>
+      <c r="D5592" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5592" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5593">
+      <c r="A5593" s="0">
+        <v>6620</v>
+      </c>
+      <c r="B5593" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5593" s="0">
+        <v>3893</v>
+      </c>
+      <c r="D5593" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5593" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5594">
+      <c r="A5594" s="0">
+        <v>6621</v>
+      </c>
+      <c r="B5594" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5594" s="0">
+        <v>3894</v>
+      </c>
+      <c r="D5594" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5594" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5595">
+      <c r="A5595" s="0">
+        <v>6622</v>
+      </c>
+      <c r="B5595" s="0">
+        <v>184</v>
+      </c>
+      <c r="C5595" s="0">
+        <v>3895</v>
+      </c>
+      <c r="D5595" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5595" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5596">
+      <c r="A5596" s="0">
+        <v>6623</v>
+      </c>
+      <c r="B5596" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5596" s="0">
+        <v>3889</v>
+      </c>
+      <c r="D5596" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5596" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5597">
+      <c r="A5597" s="0">
+        <v>6624</v>
+      </c>
+      <c r="B5597" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5597" s="0">
+        <v>3890</v>
+      </c>
+      <c r="D5597" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5597" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5598">
+      <c r="A5598" s="0">
+        <v>6625</v>
+      </c>
+      <c r="B5598" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5598" s="0">
+        <v>3891</v>
+      </c>
+      <c r="D5598" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5598" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5599">
+      <c r="A5599" s="0">
+        <v>6626</v>
+      </c>
+      <c r="B5599" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5599" s="0">
+        <v>3892</v>
+      </c>
+      <c r="D5599" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5599" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5600">
+      <c r="A5600" s="0">
+        <v>6627</v>
+      </c>
+      <c r="B5600" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5600" s="0">
+        <v>3893</v>
+      </c>
+      <c r="D5600" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5600" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5601">
+      <c r="A5601" s="0">
+        <v>6628</v>
+      </c>
+      <c r="B5601" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5601" s="0">
+        <v>3894</v>
+      </c>
+      <c r="D5601" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5601" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5602">
+      <c r="A5602" s="0">
+        <v>6629</v>
+      </c>
+      <c r="B5602" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5602" s="0">
+        <v>3895</v>
+      </c>
+      <c r="D5602" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5602" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5603">
+      <c r="A5603" s="0">
+        <v>6630</v>
+      </c>
+      <c r="B5603" s="0">
+        <v>185</v>
+      </c>
+      <c r="C5603" s="0">
+        <v>3896</v>
+      </c>
+      <c r="D5603" s="0">
+        <v>9</v>
+      </c>
+      <c r="E5603" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5604">
+      <c r="A5604" s="0">
+        <v>6631</v>
+      </c>
+      <c r="B5604" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5604" s="0">
+        <v>2140</v>
+      </c>
+      <c r="D5604" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5604" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5605">
+      <c r="A5605" s="0">
+        <v>6632</v>
+      </c>
+      <c r="B5605" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5605" s="0">
+        <v>2141</v>
+      </c>
+      <c r="D5605" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5605" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5606">
+      <c r="A5606" s="0">
+        <v>6633</v>
+      </c>
+      <c r="B5606" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5606" s="0">
+        <v>2142</v>
+      </c>
+      <c r="D5606" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5606" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5607">
+      <c r="A5607" s="0">
+        <v>6634</v>
+      </c>
+      <c r="B5607" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5607" s="0">
+        <v>2143</v>
+      </c>
+      <c r="D5607" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5607" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5608">
+      <c r="A5608" s="0">
+        <v>6635</v>
+      </c>
+      <c r="B5608" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5608" s="0">
+        <v>2144</v>
+      </c>
+      <c r="D5608" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5608" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5609">
+      <c r="A5609" s="0">
+        <v>6636</v>
+      </c>
+      <c r="B5609" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5609" s="0">
+        <v>2145</v>
+      </c>
+      <c r="D5609" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5609" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5610">
+      <c r="A5610" s="0">
+        <v>6637</v>
+      </c>
+      <c r="B5610" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5610" s="0">
+        <v>2146</v>
+      </c>
+      <c r="D5610" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5610" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5611">
+      <c r="A5611" s="0">
+        <v>6638</v>
+      </c>
+      <c r="B5611" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5611" s="0">
+        <v>3887</v>
+      </c>
+      <c r="D5611" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5611" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5612">
+      <c r="A5612" s="0">
+        <v>6639</v>
+      </c>
+      <c r="B5612" s="0">
+        <v>186</v>
+      </c>
+      <c r="C5612" s="0">
+        <v>2148</v>
+      </c>
+      <c r="D5612" s="0">
+        <v>9</v>
+      </c>
+      <c r="E5612" s="0">
+        <v>9</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5613">
+      <c r="A5613" s="0">
+        <v>6640</v>
+      </c>
+      <c r="B5613" s="0">
+        <v>187</v>
+      </c>
+      <c r="C5613" s="0">
+        <v>2315</v>
+      </c>
+      <c r="D5613" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5613" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5614">
+      <c r="A5614" s="0">
+        <v>6641</v>
+      </c>
+      <c r="B5614" s="0">
+        <v>187</v>
+      </c>
+      <c r="C5614" s="0">
+        <v>2316</v>
+      </c>
+      <c r="D5614" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5614" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5615">
+      <c r="A5615" s="0">
+        <v>6642</v>
+      </c>
+      <c r="B5615" s="0">
+        <v>187</v>
+      </c>
+      <c r="C5615" s="0">
+        <v>2140</v>
+      </c>
+      <c r="D5615" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5615" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5616">
+      <c r="A5616" s="0">
+        <v>6643</v>
+      </c>
+      <c r="B5616" s="0">
+        <v>187</v>
+      </c>
+      <c r="C5616" s="0">
+        <v>2141</v>
+      </c>
+      <c r="D5616" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5616" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5617">
+      <c r="A5617" s="0">
+        <v>6644</v>
+      </c>
+      <c r="B5617" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5617" s="0">
+        <v>3897</v>
+      </c>
+      <c r="D5617" s="0">
+        <v>1</v>
+      </c>
+      <c r="E5617" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5618">
+      <c r="A5618" s="0">
+        <v>6645</v>
+      </c>
+      <c r="B5618" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5618" s="0">
+        <v>3898</v>
+      </c>
+      <c r="D5618" s="0">
+        <v>2</v>
+      </c>
+      <c r="E5618" s="0">
+        <v>2</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5619">
+      <c r="A5619" s="0">
+        <v>6646</v>
+      </c>
+      <c r="B5619" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5619" s="0">
+        <v>3899</v>
+      </c>
+      <c r="D5619" s="0">
+        <v>3</v>
+      </c>
+      <c r="E5619" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5620">
+      <c r="A5620" s="0">
+        <v>6647</v>
+      </c>
+      <c r="B5620" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5620" s="0">
+        <v>3900</v>
+      </c>
+      <c r="D5620" s="0">
+        <v>4</v>
+      </c>
+      <c r="E5620" s="0">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5621">
+      <c r="A5621" s="0">
+        <v>6648</v>
+      </c>
+      <c r="B5621" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5621" s="0">
+        <v>3901</v>
+      </c>
+      <c r="D5621" s="0">
+        <v>5</v>
+      </c>
+      <c r="E5621" s="0">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5622">
+      <c r="A5622" s="0">
+        <v>6649</v>
+      </c>
+      <c r="B5622" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5622" s="0">
+        <v>3902</v>
+      </c>
+      <c r="D5622" s="0">
+        <v>6</v>
+      </c>
+      <c r="E5622" s="0">
+        <v>6</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5623">
+      <c r="A5623" s="0">
+        <v>6650</v>
+      </c>
+      <c r="B5623" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5623" s="0">
+        <v>3903</v>
+      </c>
+      <c r="D5623" s="0">
+        <v>7</v>
+      </c>
+      <c r="E5623" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5624">
+      <c r="A5624" s="0">
+        <v>6651</v>
+      </c>
+      <c r="B5624" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5624" s="0">
+        <v>3904</v>
+      </c>
+      <c r="D5624" s="0">
+        <v>8</v>
+      </c>
+      <c r="E5624" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5625">
+      <c r="A5625" s="0">
+        <v>6652</v>
+      </c>
+      <c r="B5625" s="0">
+        <v>188</v>
+      </c>
+      <c r="C5625" s="0">
+        <v>3905</v>
+      </c>
+      <c r="D5625" s="0">
+        <v>9</v>
+      </c>
+      <c r="E5625" s="0">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
